--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -5595,10 +5595,10 @@
         <v>396.0</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>272.0</v>
+        <v>288.0</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>124.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="120">
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="H127" s="12" t="n">
-        <v>1872.0</v>
+        <v>0.0</v>
       </c>
       <c r="I127" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>1872.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="I128" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J128" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
@@ -6316,13 +6316,13 @@
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>2808.0</v>
+        <v>936.0</v>
       </c>
       <c r="I135" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>2808.0</v>
+        <v>936.0</v>
       </c>
     </row>
     <row r="136">
@@ -6546,13 +6546,13 @@
         </is>
       </c>
       <c r="H140" s="12" t="n">
-        <v>660.0</v>
+        <v>0.0</v>
       </c>
       <c r="I140" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J140" s="12" t="n">
-        <v>660.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -6767,10 +6767,10 @@
         <v>0.0</v>
       </c>
       <c r="I145" s="12" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J145" s="12" t="n">
-        <v>-2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -6898,13 +6898,13 @@
         </is>
       </c>
       <c r="H148" s="12" t="n">
-        <v>5184.0</v>
+        <v>864.0</v>
       </c>
       <c r="I148" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J148" s="12" t="n">
         <v>864.0</v>
-      </c>
-      <c r="J148" s="12" t="n">
-        <v>4320.0</v>
       </c>
     </row>
     <row r="149">
@@ -6944,13 +6944,13 @@
         </is>
       </c>
       <c r="H149" s="12" t="n">
-        <v>5184.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I149" s="12" t="n">
         <v>5184.0</v>
       </c>
       <c r="J149" s="12" t="n">
-        <v>0.0</v>
+        <v>-864.0</v>
       </c>
     </row>
     <row r="150">
@@ -9997,10 +9997,10 @@
         <v>276.0</v>
       </c>
       <c r="I216" s="12" t="n">
-        <v>230.0</v>
+        <v>210.0</v>
       </c>
       <c r="J216" s="12" t="n">
-        <v>46.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="217">
@@ -10039,10 +10039,10 @@
         <v>0.0</v>
       </c>
       <c r="I217" s="12" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="J217" s="12" t="n">
-        <v>-6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="218">
@@ -10081,10 +10081,10 @@
         <v>0.0</v>
       </c>
       <c r="I218" s="12" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J218" s="12" t="n">
-        <v>-4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="219">
@@ -11555,10 +11555,10 @@
         <v>350.0</v>
       </c>
       <c r="I251" s="12" t="n">
-        <v>246.0</v>
+        <v>182.0</v>
       </c>
       <c r="J251" s="12" t="n">
-        <v>104.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="252">
@@ -11957,10 +11957,10 @@
         <v>276.0</v>
       </c>
       <c r="I260" s="12" t="n">
-        <v>236.0</v>
+        <v>232.0</v>
       </c>
       <c r="J260" s="12" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="261">
@@ -12095,10 +12095,10 @@
         <v>316.0</v>
       </c>
       <c r="I263" s="12" t="n">
-        <v>306.0</v>
+        <v>233.0</v>
       </c>
       <c r="J263" s="12" t="n">
-        <v>10.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="264">
@@ -15771,10 +15771,10 @@
         <v>552.0</v>
       </c>
       <c r="I347" s="12" t="n">
-        <v>126.0</v>
+        <v>42.0</v>
       </c>
       <c r="J347" s="12" t="n">
-        <v>426.0</v>
+        <v>510.0</v>
       </c>
     </row>
     <row r="348">
@@ -18623,10 +18623,10 @@
         <v>426.0</v>
       </c>
       <c r="I411" s="12" t="n">
-        <v>228.0</v>
+        <v>275.0</v>
       </c>
       <c r="J411" s="12" t="n">
-        <v>198.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="412">
@@ -18669,10 +18669,10 @@
         <v>180.0</v>
       </c>
       <c r="I412" s="12" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="J412" s="12" t="n">
-        <v>180.0</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="413">
@@ -18715,10 +18715,10 @@
         <v>300.0</v>
       </c>
       <c r="I413" s="12" t="n">
-        <v>204.0</v>
+        <v>251.0</v>
       </c>
       <c r="J413" s="12" t="n">
-        <v>96.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="414">
@@ -18761,10 +18761,10 @@
         <v>552.0</v>
       </c>
       <c r="I414" s="12" t="n">
-        <v>166.0</v>
+        <v>240.0</v>
       </c>
       <c r="J414" s="12" t="n">
-        <v>386.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="415">
@@ -19591,10 +19591,10 @@
         <v>1656.0</v>
       </c>
       <c r="I433" s="12" t="n">
-        <v>312.0</v>
+        <v>332.0</v>
       </c>
       <c r="J433" s="12" t="n">
-        <v>1344.0</v>
+        <v>1324.0</v>
       </c>
     </row>
     <row r="434">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -5592,13 +5592,13 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>396.0</v>
+        <v>0.0</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>288.0</v>
+        <v>0.0</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>108.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="H120" s="12" t="n">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>67.0</v>
+        <v>0.0</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>65.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -5676,13 +5676,13 @@
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="I121" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -6947,10 +6947,10 @@
         <v>4320.0</v>
       </c>
       <c r="I149" s="12" t="n">
-        <v>5184.0</v>
+        <v>4320.0</v>
       </c>
       <c r="J149" s="12" t="n">
-        <v>-864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="150">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -134,7 +134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J545"/>
+  <dimension ref="A1:J561"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.0" customWidth="true"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
@@ -6316,13 +6316,13 @@
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="I135" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="136">
@@ -6898,13 +6898,13 @@
         </is>
       </c>
       <c r="H148" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
       <c r="I148" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J148" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="149">
@@ -6944,13 +6944,13 @@
         </is>
       </c>
       <c r="H149" s="12" t="n">
-        <v>4320.0</v>
+        <v>0.0</v>
       </c>
       <c r="I149" s="12" t="n">
-        <v>4320.0</v>
+        <v>2592.0</v>
       </c>
       <c r="J149" s="12" t="n">
-        <v>0.0</v>
+        <v>-2592.0</v>
       </c>
     </row>
     <row r="150">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="H160" s="12" t="n">
-        <v>3744.0</v>
+        <v>0.0</v>
       </c>
       <c r="I160" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J160" s="12" t="n">
-        <v>3744.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="161">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="H183" s="12" t="n">
-        <v>3456.0</v>
+        <v>0.0</v>
       </c>
       <c r="I183" s="12" t="n">
-        <v>3456.0</v>
+        <v>2592.0</v>
       </c>
       <c r="J183" s="12" t="n">
-        <v>0.0</v>
+        <v>-2592.0</v>
       </c>
     </row>
     <row r="184">
@@ -8730,13 +8730,13 @@
         </is>
       </c>
       <c r="H188" s="12" t="n">
-        <v>6480.0</v>
+        <v>1440.0</v>
       </c>
       <c r="I188" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J188" s="12" t="n">
-        <v>6480.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="189">
@@ -8868,13 +8868,13 @@
         </is>
       </c>
       <c r="H191" s="12" t="n">
-        <v>2160.0</v>
+        <v>0.0</v>
       </c>
       <c r="I191" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J191" s="12" t="n">
-        <v>2160.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="192">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
@@ -9144,13 +9144,13 @@
         </is>
       </c>
       <c r="H197" s="12" t="n">
-        <v>3456.0</v>
+        <v>0.0</v>
       </c>
       <c r="I197" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J197" s="12" t="n">
-        <v>3456.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="198">
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="H206" s="12" t="n">
-        <v>4320.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I206" s="12" t="n">
-        <v>4320.0</v>
+        <v>1728.0</v>
       </c>
       <c r="J206" s="12" t="n">
         <v>0.0</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="H212" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="I212" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="J212" s="12" t="n">
         <v>0.0</v>
@@ -10300,13 +10300,13 @@
         </is>
       </c>
       <c r="H223" s="12" t="n">
-        <v>660.0</v>
+        <v>0.0</v>
       </c>
       <c r="I223" s="12" t="n">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
       <c r="J223" s="12" t="n">
-        <v>627.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="224">
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="H240" s="12" t="n">
-        <v>1584.0</v>
+        <v>792.0</v>
       </c>
       <c r="I240" s="12" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
       <c r="J240" s="12" t="n">
         <v>792.0</v>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
@@ -11288,13 +11288,13 @@
         </is>
       </c>
       <c r="H245" s="12" t="n">
-        <v>0.0</v>
+        <v>2808.0</v>
       </c>
       <c r="I245" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J245" s="12" t="n">
-        <v>0.0</v>
+        <v>2808.0</v>
       </c>
     </row>
     <row r="246">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
@@ -11334,13 +11334,13 @@
         </is>
       </c>
       <c r="H246" s="12" t="n">
-        <v>4680.0</v>
+        <v>0.0</v>
       </c>
       <c r="I246" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J246" s="12" t="n">
-        <v>4680.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="247">
@@ -12015,10 +12015,10 @@
         <v>350.0</v>
       </c>
       <c r="I261" s="12" t="n">
-        <v>182.0</v>
+        <v>176.0</v>
       </c>
       <c r="J261" s="12" t="n">
-        <v>168.0</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="262">
@@ -12509,10 +12509,10 @@
         <v>276.0</v>
       </c>
       <c r="I272" s="12" t="n">
-        <v>232.0</v>
+        <v>224.0</v>
       </c>
       <c r="J272" s="12" t="n">
-        <v>44.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="273">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
@@ -12824,13 +12824,13 @@
         </is>
       </c>
       <c r="H279" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="I279" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="280">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
@@ -12870,13 +12870,13 @@
         </is>
       </c>
       <c r="H280" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
       <c r="I280" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J280" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
     </row>
     <row r="281">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
@@ -13368,13 +13368,13 @@
         </is>
       </c>
       <c r="H291" s="12" t="n">
-        <v>0.0</v>
+        <v>19008.0</v>
       </c>
       <c r="I291" s="12" t="n">
-        <v>0.0</v>
+        <v>12960.0</v>
       </c>
       <c r="J291" s="12" t="n">
-        <v>0.0</v>
+        <v>6048.0</v>
       </c>
     </row>
     <row r="292">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
@@ -13414,13 +13414,13 @@
         </is>
       </c>
       <c r="H292" s="12" t="n">
-        <v>19008.0</v>
+        <v>0.0</v>
       </c>
       <c r="I292" s="12" t="n">
-        <v>12960.0</v>
+        <v>0.0</v>
       </c>
       <c r="J292" s="12" t="n">
-        <v>6048.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="293">
@@ -13926,7 +13926,7 @@
       <c r="B304" s="12"/>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
@@ -13968,7 +13968,7 @@
       <c r="B305" s="12"/>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
@@ -15361,10 +15361,10 @@
         <v>1584.0</v>
       </c>
       <c r="I336" s="12" t="n">
-        <v>504.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J336" s="12" t="n">
-        <v>1080.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="337">
@@ -15403,10 +15403,10 @@
         <v>720.0</v>
       </c>
       <c r="I337" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J337" s="12" t="n">
         <v>720.0</v>
-      </c>
-      <c r="J337" s="12" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="338">
@@ -15855,10 +15855,10 @@
         <v>3960.0</v>
       </c>
       <c r="I347" s="12" t="n">
-        <v>3960.0</v>
+        <v>3816.0</v>
       </c>
       <c r="J347" s="12" t="n">
-        <v>0.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="348">
@@ -15958,7 +15958,7 @@
       <c r="B350" s="12"/>
       <c r="C350" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D350" s="12" t="inlineStr">
@@ -16000,7 +16000,7 @@
       <c r="B351" s="12"/>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D351" s="12" t="inlineStr">
@@ -16153,10 +16153,10 @@
         <v>0.0</v>
       </c>
       <c r="I354" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="J354" s="12" t="n">
-        <v>-936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="355">
@@ -16386,7 +16386,7 @@
       <c r="B360" s="12"/>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D360" s="12" t="inlineStr">
@@ -16410,13 +16410,13 @@
         </is>
       </c>
       <c r="H360" s="12" t="n">
-        <v>1728.0</v>
+        <v>9504.0</v>
       </c>
       <c r="I360" s="12" t="n">
-        <v>864.0</v>
+        <v>5184.0</v>
       </c>
       <c r="J360" s="12" t="n">
-        <v>864.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="361">
@@ -16428,7 +16428,7 @@
       <c r="B361" s="12"/>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D361" s="12" t="inlineStr">
@@ -16452,13 +16452,13 @@
         </is>
       </c>
       <c r="H361" s="12" t="n">
-        <v>9504.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I361" s="12" t="n">
-        <v>5184.0</v>
+        <v>864.0</v>
       </c>
       <c r="J361" s="12" t="n">
-        <v>4320.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="362">
@@ -16722,7 +16722,7 @@
       <c r="B368" s="12"/>
       <c r="C368" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D368" s="12" t="inlineStr">
@@ -16746,13 +16746,13 @@
         </is>
       </c>
       <c r="H368" s="12" t="n">
-        <v>1584.0</v>
+        <v>3168.0</v>
       </c>
       <c r="I368" s="12" t="n">
-        <v>0.0</v>
+        <v>3024.0</v>
       </c>
       <c r="J368" s="12" t="n">
-        <v>1584.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="369">
@@ -16764,7 +16764,7 @@
       <c r="B369" s="12"/>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D369" s="12" t="inlineStr">
@@ -16788,13 +16788,13 @@
         </is>
       </c>
       <c r="H369" s="12" t="n">
-        <v>3168.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I369" s="12" t="n">
-        <v>3024.0</v>
+        <v>0.0</v>
       </c>
       <c r="J369" s="12" t="n">
-        <v>144.0</v>
+        <v>1584.0</v>
       </c>
     </row>
     <row r="370">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="C405" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D405" s="12" t="inlineStr">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="C406" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D406" s="12" t="inlineStr">
@@ -18621,10 +18621,10 @@
         <v>2808.0</v>
       </c>
       <c r="I410" s="12" t="n">
-        <v>2808.0</v>
+        <v>1872.0</v>
       </c>
       <c r="J410" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
     </row>
     <row r="411">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="C414" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D414" s="12" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="C415" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D415" s="12" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="C416" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D416" s="12" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="C417" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D417" s="12" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="C420" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D420" s="12" t="inlineStr">
@@ -19078,13 +19078,13 @@
         </is>
       </c>
       <c r="H420" s="12" t="n">
-        <v>9504.0</v>
+        <v>0.0</v>
       </c>
       <c r="I420" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J420" s="12" t="n">
-        <v>9504.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="421">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C421" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D421" s="12" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="C422" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D422" s="12" t="inlineStr">
@@ -19170,13 +19170,13 @@
         </is>
       </c>
       <c r="H422" s="12" t="n">
-        <v>0.0</v>
+        <v>9504.0</v>
       </c>
       <c r="I422" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J422" s="12" t="n">
-        <v>0.0</v>
+        <v>9504.0</v>
       </c>
     </row>
     <row r="423">
@@ -19383,10 +19383,10 @@
         <v>8640.0</v>
       </c>
       <c r="I427" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J427" s="12" t="n">
         <v>8640.0</v>
-      </c>
-      <c r="J427" s="12" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="428">
@@ -19689,10 +19689,10 @@
         <v>3600.0</v>
       </c>
       <c r="I434" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J434" s="12" t="n">
         <v>3600.0</v>
-      </c>
-      <c r="J434" s="12" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="435">
@@ -19953,10 +19953,10 @@
         <v>4320.0</v>
       </c>
       <c r="I440" s="12" t="n">
-        <v>3600.0</v>
+        <v>0.0</v>
       </c>
       <c r="J440" s="12" t="n">
-        <v>720.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="441">
@@ -21289,10 +21289,10 @@
         <v>1584.0</v>
       </c>
       <c r="I470" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
       <c r="J470" s="12" t="n">
-        <v>720.0</v>
+        <v>1584.0</v>
       </c>
     </row>
     <row r="471">
@@ -21432,18 +21432,18 @@
     <row r="474">
       <c r="A474" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
+          <t>GF0700002001</t>
         </is>
       </c>
       <c r="B474" s="12"/>
       <c r="C474" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D474" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,+0.4/-0.2m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E474" s="12" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="F474" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G474" s="12" t="inlineStr">
@@ -21462,40 +21462,40 @@
         </is>
       </c>
       <c r="H474" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="I474" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J474" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="12" t="inlineStr">
         <is>
-          <t>GF0700000940</t>
+          <t>GF0700002015</t>
         </is>
       </c>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D475" s="12" t="inlineStr">
         <is>
-          <t>ODM Battery, 5 kWh, Medium Voltage, LFP, Outdoor IP65, IEC, 10 years Product Warranty</t>
+          <t>TOPCon+Half-Cuts,+0.4/-0.2m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E475" s="12" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F475" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G475" s="12" t="inlineStr">
@@ -21504,25 +21504,25 @@
         </is>
       </c>
       <c r="H475" s="12" t="n">
-        <v>1656.0</v>
+        <v>4158.0</v>
       </c>
       <c r="I475" s="12" t="n">
-        <v>332.0</v>
+        <v>0.0</v>
       </c>
       <c r="J475" s="12" t="n">
-        <v>1324.0</v>
+        <v>4158.0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="12" t="inlineStr">
         <is>
-          <t>GF0700000077</t>
+          <t>GF0700000071</t>
         </is>
       </c>
       <c r="B476" s="12"/>
       <c r="C476" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D476" s="12" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="F476" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G476" s="12" t="inlineStr">
@@ -21546,30 +21546,30 @@
         </is>
       </c>
       <c r="H476" s="12" t="n">
-        <v>5616.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I476" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J476" s="12" t="n">
-        <v>5616.0</v>
+        <v>5184.0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
+          <t>GF0700000881</t>
         </is>
       </c>
       <c r="B477" s="12"/>
       <c r="C477" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D477" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E477" s="12" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="F477" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G477" s="12" t="inlineStr">
@@ -21588,40 +21588,40 @@
         </is>
       </c>
       <c r="H477" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
       <c r="I477" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J477" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
+          <t>GF0700000940</t>
         </is>
       </c>
       <c r="B478" s="12"/>
       <c r="C478" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D478" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>ODM Battery, 5 kWh, Medium Voltage, LFP, Outdoor IP65, IEC, 10 years Product Warranty</t>
         </is>
       </c>
       <c r="E478" s="12" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="F478" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G478" s="12" t="inlineStr">
@@ -21630,30 +21630,30 @@
         </is>
       </c>
       <c r="H478" s="12" t="n">
-        <v>0.0</v>
+        <v>1656.0</v>
       </c>
       <c r="I478" s="12" t="n">
-        <v>0.0</v>
+        <v>332.0</v>
       </c>
       <c r="J478" s="12" t="n">
-        <v>0.0</v>
+        <v>1324.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="12" t="inlineStr">
         <is>
-          <t>GF0101010096</t>
+          <t>GF0700001535</t>
         </is>
       </c>
       <c r="B479" s="12"/>
       <c r="C479" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D479" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>PVM,HSM-NT48-JH470-CFP</t>
         </is>
       </c>
       <c r="E479" s="12" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="F479" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G479" s="12" t="inlineStr">
@@ -21672,30 +21672,30 @@
         </is>
       </c>
       <c r="H479" s="12" t="n">
-        <v>1440.0</v>
+        <v>5616.0</v>
       </c>
       <c r="I479" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J479" s="12" t="n">
-        <v>1440.0</v>
+        <v>5616.0</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
+          <t>GF0700001601</t>
         </is>
       </c>
       <c r="B480" s="12"/>
       <c r="C480" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D480" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.2m,Black Frame,White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E480" s="12" t="inlineStr">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="F480" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G480" s="12" t="inlineStr">
@@ -21714,19 +21714,19 @@
         </is>
       </c>
       <c r="H480" s="12" t="n">
-        <v>9360.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I480" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J480" s="12" t="n">
-        <v>9360.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="12" t="inlineStr">
         <is>
-          <t>GF0700002016</t>
+          <t>GF0700000077</t>
         </is>
       </c>
       <c r="B481" s="12"/>
@@ -21737,7 +21737,7 @@
       </c>
       <c r="D481" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,+0.4/-0.2m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E481" s="12" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="F481" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G481" s="12" t="inlineStr">
@@ -21756,19 +21756,19 @@
         </is>
       </c>
       <c r="H481" s="12" t="n">
-        <v>5346.0</v>
+        <v>5616.0</v>
       </c>
       <c r="I481" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J481" s="12" t="n">
-        <v>5346.0</v>
+        <v>5616.0</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
+          <t>GF0700001907</t>
         </is>
       </c>
       <c r="B482" s="12"/>
@@ -21779,7 +21779,7 @@
       </c>
       <c r="D482" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E482" s="12" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="F482" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G482" s="12" t="inlineStr">
@@ -21798,30 +21798,30 @@
         </is>
       </c>
       <c r="H482" s="12" t="n">
-        <v>4320.0</v>
+        <v>2376.0</v>
       </c>
       <c r="I482" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J482" s="12" t="n">
-        <v>4320.0</v>
+        <v>2376.0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="12" t="inlineStr">
         <is>
-          <t>GF0700002074</t>
+          <t>GF0700002042</t>
         </is>
       </c>
       <c r="B483" s="12"/>
       <c r="C483" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D483" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E483" s="12" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="F483" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G483" s="12" t="inlineStr">
@@ -21840,19 +21840,19 @@
         </is>
       </c>
       <c r="H483" s="12" t="n">
-        <v>9360.0</v>
+        <v>0.0</v>
       </c>
       <c r="I483" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J483" s="12" t="n">
-        <v>9360.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="12" t="inlineStr">
         <is>
-          <t>GF0700002080</t>
+          <t>GF0101010096</t>
         </is>
       </c>
       <c r="B484" s="12"/>
@@ -21863,7 +21863,7 @@
       </c>
       <c r="D484" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E484" s="12" t="inlineStr">
@@ -21894,18 +21894,18 @@
     <row r="485">
       <c r="A485" s="12" t="inlineStr">
         <is>
-          <t>GF0700002073</t>
+          <t>GF0700000078</t>
         </is>
       </c>
       <c r="B485" s="12"/>
       <c r="C485" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D485" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E485" s="12" t="inlineStr">
@@ -21915,39 +21915,39 @@
       </c>
       <c r="F485" s="12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H485" s="12" t="n">
-        <v>2808.0</v>
+        <v>9360.0</v>
       </c>
       <c r="I485" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J485" s="12" t="n">
-        <v>2808.0</v>
+        <v>9360.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="12" t="inlineStr">
         <is>
-          <t>GF0700002074</t>
+          <t>GF0700002001</t>
         </is>
       </c>
       <c r="B486" s="12"/>
       <c r="C486" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D486" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,+0.4/-0.2m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E486" s="12" t="inlineStr">
@@ -21957,39 +21957,39 @@
       </c>
       <c r="F486" s="12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H486" s="12" t="n">
-        <v>1872.0</v>
+        <v>720.0</v>
       </c>
       <c r="I486" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J486" s="12" t="n">
-        <v>1872.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
+          <t>GF0700002016</t>
         </is>
       </c>
       <c r="B487" s="12"/>
       <c r="C487" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D487" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,+0.4/-0.2m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E487" s="12" t="inlineStr">
@@ -21999,39 +21999,39 @@
       </c>
       <c r="F487" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H487" s="12" t="n">
-        <v>0.0</v>
+        <v>5346.0</v>
       </c>
       <c r="I487" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J487" s="12" t="n">
-        <v>0.0</v>
+        <v>5346.0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
+          <t>GF0700002042</t>
         </is>
       </c>
       <c r="B488" s="12"/>
       <c r="C488" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D488" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E488" s="12" t="inlineStr">
@@ -22041,39 +22041,39 @@
       </c>
       <c r="F488" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H488" s="12" t="n">
-        <v>0.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I488" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J488" s="12" t="n">
-        <v>0.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="12" t="inlineStr">
         <is>
-          <t>GF0700000071</t>
+          <t>GF0700002074</t>
         </is>
       </c>
       <c r="B489" s="12"/>
       <c r="C489" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D489" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E489" s="12" t="inlineStr">
@@ -22083,43 +22083,39 @@
       </c>
       <c r="F489" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H489" s="12" t="n">
-        <v>864.0</v>
+        <v>9360.0</v>
       </c>
       <c r="I489" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J489" s="12" t="n">
-        <v>864.0</v>
+        <v>9360.0</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
-        </is>
-      </c>
-      <c r="B490" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505-CFP</t>
-        </is>
-      </c>
+          <t>GF0700002080</t>
+        </is>
+      </c>
+      <c r="B490" s="12"/>
       <c r="C490" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D490" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E490" s="12" t="inlineStr">
@@ -22129,39 +22125,39 @@
       </c>
       <c r="F490" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 42</t>
+          <t>2026 Week 41</t>
         </is>
       </c>
       <c r="H490" s="12" t="n">
-        <v>1728.0</v>
+        <v>1440.0</v>
       </c>
       <c r="I490" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
       <c r="J490" s="12" t="n">
-        <v>864.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="12" t="inlineStr">
         <is>
-          <t>GF0700000071</t>
+          <t>GF0700002073</t>
         </is>
       </c>
       <c r="B491" s="12"/>
       <c r="C491" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D491" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E491" s="12" t="inlineStr">
@@ -22171,7 +22167,7 @@
       </c>
       <c r="F491" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G491" s="12" t="inlineStr">
@@ -22180,30 +22176,30 @@
         </is>
       </c>
       <c r="H491" s="12" t="n">
-        <v>5184.0</v>
+        <v>2808.0</v>
       </c>
       <c r="I491" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J491" s="12" t="n">
-        <v>5184.0</v>
+        <v>2808.0</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="12" t="inlineStr">
         <is>
-          <t>GF0700001817</t>
+          <t>GF0700002074</t>
         </is>
       </c>
       <c r="B492" s="12"/>
       <c r="C492" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D492" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E492" s="12" t="inlineStr">
@@ -22213,7 +22209,7 @@
       </c>
       <c r="F492" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G492" s="12" t="inlineStr">
@@ -22222,30 +22218,30 @@
         </is>
       </c>
       <c r="H492" s="12" t="n">
-        <v>720.0</v>
+        <v>1872.0</v>
       </c>
       <c r="I492" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J492" s="12" t="n">
-        <v>720.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="12" t="inlineStr">
         <is>
-          <t>GF0700002066</t>
+          <t>GF0700000076</t>
         </is>
       </c>
       <c r="B493" s="12"/>
       <c r="C493" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D493" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E493" s="12" t="inlineStr">
@@ -22255,7 +22251,7 @@
       </c>
       <c r="F493" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G493" s="12" t="inlineStr">
@@ -22276,18 +22272,18 @@
     <row r="494">
       <c r="A494" s="12" t="inlineStr">
         <is>
-          <t>GF0700002080</t>
+          <t>GF0700000078</t>
         </is>
       </c>
       <c r="B494" s="12"/>
       <c r="C494" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D494" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E494" s="12" t="inlineStr">
@@ -22297,7 +22293,7 @@
       </c>
       <c r="F494" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G494" s="12" t="inlineStr">
@@ -22306,25 +22302,25 @@
         </is>
       </c>
       <c r="H494" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
       <c r="I494" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J494" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
+          <t>GF0700000071</t>
         </is>
       </c>
       <c r="B495" s="12"/>
       <c r="C495" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D495" s="12" t="inlineStr">
@@ -22339,7 +22335,7 @@
       </c>
       <c r="F495" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G495" s="12" t="inlineStr">
@@ -22348,30 +22344,34 @@
         </is>
       </c>
       <c r="H495" s="12" t="n">
-        <v>12168.0</v>
+        <v>864.0</v>
       </c>
       <c r="I495" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J495" s="12" t="n">
-        <v>12168.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
-        </is>
-      </c>
-      <c r="B496" s="12"/>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B496" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505-CFP</t>
+        </is>
+      </c>
       <c r="C496" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D496" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E496" s="12" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="F496" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G496" s="12" t="inlineStr">
@@ -22390,19 +22390,19 @@
         </is>
       </c>
       <c r="H496" s="12" t="n">
-        <v>0.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I496" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="J496" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="12" t="inlineStr">
         <is>
-          <t>GF0101010096</t>
+          <t>GF0700000071</t>
         </is>
       </c>
       <c r="B497" s="12"/>
@@ -22413,7 +22413,7 @@
       </c>
       <c r="D497" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E497" s="12" t="inlineStr">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="F497" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G497" s="12" t="inlineStr">
@@ -22432,25 +22432,25 @@
         </is>
       </c>
       <c r="H497" s="12" t="n">
-        <v>4320.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I497" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J497" s="12" t="n">
-        <v>4320.0</v>
+        <v>5184.0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
+          <t>GF0700000071</t>
         </is>
       </c>
       <c r="B498" s="12"/>
       <c r="C498" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D498" s="12" t="inlineStr">
@@ -22465,7 +22465,7 @@
       </c>
       <c r="F498" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G498" s="12" t="inlineStr">
@@ -22474,30 +22474,30 @@
         </is>
       </c>
       <c r="H498" s="12" t="n">
-        <v>10368.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I498" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J498" s="12" t="n">
-        <v>10368.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="12" t="inlineStr">
         <is>
-          <t>GF0700000077</t>
+          <t>GF0700001536</t>
         </is>
       </c>
       <c r="B499" s="12"/>
       <c r="C499" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D499" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>PVM,HSM-NT48-JH475-CFP</t>
         </is>
       </c>
       <c r="E499" s="12" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="F499" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G499" s="12" t="inlineStr">
@@ -22516,19 +22516,19 @@
         </is>
       </c>
       <c r="H499" s="12" t="n">
-        <v>2808.0</v>
+        <v>11232.0</v>
       </c>
       <c r="I499" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J499" s="12" t="n">
-        <v>2808.0</v>
+        <v>11232.0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
+          <t>GF0700001817</t>
         </is>
       </c>
       <c r="B500" s="12"/>
@@ -22539,7 +22539,7 @@
       </c>
       <c r="D500" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E500" s="12" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="F500" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G500" s="12" t="inlineStr">
@@ -22558,30 +22558,30 @@
         </is>
       </c>
       <c r="H500" s="12" t="n">
-        <v>2808.0</v>
+        <v>720.0</v>
       </c>
       <c r="I500" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J500" s="12" t="n">
-        <v>2808.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="12" t="inlineStr">
         <is>
-          <t>GF0700000346</t>
+          <t>GF0700002066</t>
         </is>
       </c>
       <c r="B501" s="12"/>
       <c r="C501" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D501" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E501" s="12" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="F501" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G501" s="12" t="inlineStr">
@@ -22600,19 +22600,19 @@
         </is>
       </c>
       <c r="H501" s="12" t="n">
-        <v>3600.0</v>
+        <v>0.0</v>
       </c>
       <c r="I501" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J501" s="12" t="n">
-        <v>3600.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="12" t="inlineStr">
         <is>
-          <t>GF0700001817</t>
+          <t>GF0700002080</t>
         </is>
       </c>
       <c r="B502" s="12"/>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="D502" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E502" s="12" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="F502" s="12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G502" s="12" t="inlineStr">
@@ -22642,34 +22642,30 @@
         </is>
       </c>
       <c r="H502" s="12" t="n">
-        <v>2880.0</v>
+        <v>720.0</v>
       </c>
       <c r="I502" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J502" s="12" t="n">
-        <v>2880.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
-        </is>
-      </c>
-      <c r="B503" s="12" t="inlineStr">
-        <is>
-          <t>HSM-BD66-GR650</t>
-        </is>
-      </c>
+          <t>GF0700000078</t>
+        </is>
+      </c>
+      <c r="B503" s="12"/>
       <c r="C503" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D503" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E503" s="12" t="inlineStr">
@@ -22679,43 +22675,39 @@
       </c>
       <c r="F503" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G503" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H503" s="12" t="n">
-        <v>2880.0</v>
+        <v>12168.0</v>
       </c>
       <c r="I503" s="12" t="n">
-        <v>2880.0</v>
+        <v>0.0</v>
       </c>
       <c r="J503" s="12" t="n">
-        <v>0.0</v>
+        <v>12168.0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
-        </is>
-      </c>
-      <c r="B504" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND48-DR450</t>
-        </is>
-      </c>
+          <t>GF0700002042</t>
+        </is>
+      </c>
+      <c r="B504" s="12"/>
       <c r="C504" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D504" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E504" s="12" t="inlineStr">
@@ -22725,43 +22717,39 @@
       </c>
       <c r="F504" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G504" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H504" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="I504" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J504" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="12" t="inlineStr">
         <is>
-          <t>GF0700000071</t>
-        </is>
-      </c>
-      <c r="B505" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR500</t>
-        </is>
-      </c>
+          <t>GF0101010096</t>
+        </is>
+      </c>
+      <c r="B505" s="12"/>
       <c r="C505" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D505" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E505" s="12" t="inlineStr">
@@ -22771,22 +22759,22 @@
       </c>
       <c r="F505" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G505" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H505" s="12" t="n">
-        <v>864.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I505" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J505" s="12" t="n">
-        <v>864.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="506">
@@ -22795,14 +22783,10 @@
           <t>GF0700000076</t>
         </is>
       </c>
-      <c r="B506" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505</t>
-        </is>
-      </c>
+      <c r="B506" s="12"/>
       <c r="C506" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D506" s="12" t="inlineStr">
@@ -22817,38 +22801,34 @@
       </c>
       <c r="F506" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G506" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H506" s="12" t="n">
-        <v>864.0</v>
+        <v>10368.0</v>
       </c>
       <c r="I506" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J506" s="12" t="n">
-        <v>864.0</v>
+        <v>10368.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
-        </is>
-      </c>
-      <c r="B507" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505-CFP</t>
-        </is>
-      </c>
+          <t>GF0700000077</t>
+        </is>
+      </c>
+      <c r="B507" s="12"/>
       <c r="C507" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D507" s="12" t="inlineStr">
@@ -22863,34 +22843,34 @@
       </c>
       <c r="F507" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G507" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H507" s="12" t="n">
-        <v>5184.0</v>
+        <v>2808.0</v>
       </c>
       <c r="I507" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J507" s="12" t="n">
-        <v>5184.0</v>
+        <v>2808.0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
+          <t>GF0700000078</t>
         </is>
       </c>
       <c r="B508" s="12"/>
       <c r="C508" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D508" s="12" t="inlineStr">
@@ -22905,39 +22885,39 @@
       </c>
       <c r="F508" s="12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G508" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H508" s="12" t="n">
-        <v>864.0</v>
+        <v>2808.0</v>
       </c>
       <c r="I508" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J508" s="12" t="n">
-        <v>864.0</v>
+        <v>2808.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
+          <t>GF0700000346</t>
         </is>
       </c>
       <c r="B509" s="12"/>
       <c r="C509" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D509" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E509" s="12" t="inlineStr">
@@ -22947,39 +22927,39 @@
       </c>
       <c r="F509" s="12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G509" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H509" s="12" t="n">
-        <v>0.0</v>
+        <v>3600.0</v>
       </c>
       <c r="I509" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J509" s="12" t="n">
-        <v>0.0</v>
+        <v>3600.0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="12" t="inlineStr">
         <is>
-          <t>GF0700000795</t>
+          <t>GF0700001817</t>
         </is>
       </c>
       <c r="B510" s="12"/>
       <c r="C510" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D510" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E510" s="12" t="inlineStr">
@@ -22989,39 +22969,43 @@
       </c>
       <c r="F510" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G510" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 43</t>
+          <t>2026 Week 42</t>
         </is>
       </c>
       <c r="H510" s="12" t="n">
-        <v>2376.0</v>
+        <v>2880.0</v>
       </c>
       <c r="I510" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J510" s="12" t="n">
-        <v>2376.0</v>
+        <v>2880.0</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="12" t="inlineStr">
         <is>
-          <t>GF0700001536</t>
-        </is>
-      </c>
-      <c r="B511" s="12"/>
+          <t>GF0700002042</t>
+        </is>
+      </c>
+      <c r="B511" s="12" t="inlineStr">
+        <is>
+          <t>HSM-BD66-GR650</t>
+        </is>
+      </c>
       <c r="C511" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D511" s="12" t="inlineStr">
         <is>
-          <t>PVM,HSM-NT48-JH475-CFP</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E511" s="12" t="inlineStr">
@@ -23031,7 +23015,7 @@
       </c>
       <c r="F511" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G511" s="12" t="inlineStr">
@@ -23040,30 +23024,34 @@
         </is>
       </c>
       <c r="H511" s="12" t="n">
-        <v>936.0</v>
+        <v>2880.0</v>
       </c>
       <c r="I511" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J511" s="12" t="n">
-        <v>936.0</v>
+        <v>2880.0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="12" t="inlineStr">
         <is>
-          <t>GF0700001539</t>
-        </is>
-      </c>
-      <c r="B512" s="12"/>
+          <t>GF0700000078</t>
+        </is>
+      </c>
+      <c r="B512" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND48-DR450</t>
+        </is>
+      </c>
       <c r="C512" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D512" s="12" t="inlineStr">
         <is>
-          <t>PVM,HSM-NT48-HH465</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E512" s="12" t="inlineStr">
@@ -23073,7 +23061,7 @@
       </c>
       <c r="F512" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G512" s="12" t="inlineStr">
@@ -23082,30 +23070,34 @@
         </is>
       </c>
       <c r="H512" s="12" t="n">
-        <v>4680.0</v>
+        <v>936.0</v>
       </c>
       <c r="I512" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J512" s="12" t="n">
-        <v>4680.0</v>
+        <v>936.0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B513" s="12"/>
+          <t>GF0700000071</t>
+        </is>
+      </c>
+      <c r="B513" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR500</t>
+        </is>
+      </c>
       <c r="C513" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D513" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E513" s="12" t="inlineStr">
@@ -23115,7 +23107,7 @@
       </c>
       <c r="F513" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G513" s="12" t="inlineStr">
@@ -23124,30 +23116,34 @@
         </is>
       </c>
       <c r="H513" s="12" t="n">
-        <v>792.0</v>
+        <v>864.0</v>
       </c>
       <c r="I513" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J513" s="12" t="n">
-        <v>792.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B514" s="12"/>
+          <t>GF0700000076</t>
+        </is>
+      </c>
+      <c r="B514" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505</t>
+        </is>
+      </c>
       <c r="C514" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D514" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E514" s="12" t="inlineStr">
@@ -23157,7 +23153,7 @@
       </c>
       <c r="F514" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G514" s="12" t="inlineStr">
@@ -23166,30 +23162,34 @@
         </is>
       </c>
       <c r="H514" s="12" t="n">
-        <v>1584.0</v>
+        <v>864.0</v>
       </c>
       <c r="I514" s="12" t="n">
-        <v>1548.0</v>
+        <v>0.0</v>
       </c>
       <c r="J514" s="12" t="n">
-        <v>36.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B515" s="12"/>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B515" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505-CFP</t>
+        </is>
+      </c>
       <c r="C515" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D515" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E515" s="12" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="F515" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G515" s="12" t="inlineStr">
@@ -23208,30 +23208,30 @@
         </is>
       </c>
       <c r="H515" s="12" t="n">
-        <v>2376.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I515" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J515" s="12" t="n">
-        <v>2376.0</v>
+        <v>5184.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
+          <t>GF0700000076</t>
         </is>
       </c>
       <c r="B516" s="12"/>
       <c r="C516" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D516" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E516" s="12" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="F516" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G516" s="12" t="inlineStr">
@@ -23250,29 +23250,25 @@
         </is>
       </c>
       <c r="H516" s="12" t="n">
-        <v>2880.0</v>
+        <v>864.0</v>
       </c>
       <c r="I516" s="12" t="n">
-        <v>2880.0</v>
+        <v>0.0</v>
       </c>
       <c r="J516" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
-        </is>
-      </c>
-      <c r="B517" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND48-DR450</t>
-        </is>
-      </c>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B517" s="12"/>
       <c r="C517" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D517" s="12" t="inlineStr">
@@ -23287,7 +23283,7 @@
       </c>
       <c r="F517" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G517" s="12" t="inlineStr">
@@ -23296,26 +23292,22 @@
         </is>
       </c>
       <c r="H517" s="12" t="n">
-        <v>4680.0</v>
+        <v>0.0</v>
       </c>
       <c r="I517" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J517" s="12" t="n">
-        <v>4680.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="12" t="inlineStr">
         <is>
-          <t>GF0700000880</t>
-        </is>
-      </c>
-      <c r="B518" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR500-CFP</t>
-        </is>
-      </c>
+          <t>GF0700000795</t>
+        </is>
+      </c>
+      <c r="B518" s="12"/>
       <c r="C518" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -23323,7 +23315,7 @@
       </c>
       <c r="D518" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E518" s="12" t="inlineStr">
@@ -23333,7 +23325,7 @@
       </c>
       <c r="F518" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G518" s="12" t="inlineStr">
@@ -23342,34 +23334,30 @@
         </is>
       </c>
       <c r="H518" s="12" t="n">
-        <v>0.0</v>
+        <v>2376.0</v>
       </c>
       <c r="I518" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J518" s="12" t="n">
-        <v>0.0</v>
+        <v>2376.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
-        </is>
-      </c>
-      <c r="B519" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505</t>
-        </is>
-      </c>
+          <t>GF0700001536</t>
+        </is>
+      </c>
+      <c r="B519" s="12"/>
       <c r="C519" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D519" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>PVM,HSM-NT48-JH475-CFP</t>
         </is>
       </c>
       <c r="E519" s="12" t="inlineStr">
@@ -23379,7 +23367,7 @@
       </c>
       <c r="F519" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G519" s="12" t="inlineStr">
@@ -23388,26 +23376,22 @@
         </is>
       </c>
       <c r="H519" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
       <c r="I519" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J519" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
-        </is>
-      </c>
-      <c r="B520" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505</t>
-        </is>
-      </c>
+          <t>GF0700001539</t>
+        </is>
+      </c>
+      <c r="B520" s="12"/>
       <c r="C520" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -23415,7 +23399,7 @@
       </c>
       <c r="D520" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>PVM,HSM-NT48-HH465</t>
         </is>
       </c>
       <c r="E520" s="12" t="inlineStr">
@@ -23425,7 +23409,7 @@
       </c>
       <c r="F520" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G520" s="12" t="inlineStr">
@@ -23434,26 +23418,22 @@
         </is>
       </c>
       <c r="H520" s="12" t="n">
-        <v>0.0</v>
+        <v>4680.0</v>
       </c>
       <c r="I520" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J520" s="12" t="n">
-        <v>0.0</v>
+        <v>4680.0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
-        </is>
-      </c>
-      <c r="B521" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505-CFP</t>
-        </is>
-      </c>
+          <t>GF0700001601</t>
+        </is>
+      </c>
+      <c r="B521" s="12"/>
       <c r="C521" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -23461,7 +23441,7 @@
       </c>
       <c r="D521" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.2m,Black Frame,White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E521" s="12" t="inlineStr">
@@ -23471,7 +23451,7 @@
       </c>
       <c r="F521" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G521" s="12" t="inlineStr">
@@ -23480,34 +23460,30 @@
         </is>
       </c>
       <c r="H521" s="12" t="n">
-        <v>0.0</v>
+        <v>2592.0</v>
       </c>
       <c r="I521" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J521" s="12" t="n">
-        <v>0.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="12" t="inlineStr">
         <is>
-          <t>GF0700001817</t>
-        </is>
-      </c>
-      <c r="B522" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND66-GR620</t>
-        </is>
-      </c>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B522" s="12"/>
       <c r="C522" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D522" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E522" s="12" t="inlineStr">
@@ -23517,7 +23493,7 @@
       </c>
       <c r="F522" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G522" s="12" t="inlineStr">
@@ -23526,34 +23502,30 @@
         </is>
       </c>
       <c r="H522" s="12" t="n">
-        <v>0.0</v>
+        <v>792.0</v>
       </c>
       <c r="I522" s="12" t="n">
-        <v>0.0</v>
+        <v>216.0</v>
       </c>
       <c r="J522" s="12" t="n">
-        <v>0.0</v>
+        <v>576.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="12" t="inlineStr">
         <is>
-          <t>GF0101010096</t>
-        </is>
-      </c>
-      <c r="B523" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND66-GR625</t>
-        </is>
-      </c>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B523" s="12"/>
       <c r="C523" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D523" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E523" s="12" t="inlineStr">
@@ -23563,7 +23535,7 @@
       </c>
       <c r="F523" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G523" s="12" t="inlineStr">
@@ -23572,13 +23544,13 @@
         </is>
       </c>
       <c r="H523" s="12" t="n">
-        <v>0.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I523" s="12" t="n">
-        <v>0.0</v>
+        <v>1548.0</v>
       </c>
       <c r="J523" s="12" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="524">
@@ -23587,14 +23559,10 @@
           <t>GF0700001907</t>
         </is>
       </c>
-      <c r="B524" s="12" t="inlineStr">
-        <is>
-          <t>SPR-P7-515-BLK-P</t>
-        </is>
-      </c>
+      <c r="B524" s="12"/>
       <c r="C524" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D524" s="12" t="inlineStr">
@@ -23618,30 +23586,30 @@
         </is>
       </c>
       <c r="H524" s="12" t="n">
-        <v>0.0</v>
+        <v>2376.0</v>
       </c>
       <c r="I524" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J524" s="12" t="n">
-        <v>0.0</v>
+        <v>2376.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="12" t="inlineStr">
         <is>
-          <t>GF0101010096</t>
+          <t>GF0700002042</t>
         </is>
       </c>
       <c r="B525" s="12"/>
       <c r="C525" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D525" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E525" s="12" t="inlineStr">
@@ -23651,34 +23619,38 @@
       </c>
       <c r="F525" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G525" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H525" s="12" t="n">
-        <v>3600.0</v>
+        <v>2880.0</v>
       </c>
       <c r="I525" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J525" s="12" t="n">
-        <v>3600.0</v>
+        <v>2880.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
-        </is>
-      </c>
-      <c r="B526" s="12"/>
+          <t>GF0700000078</t>
+        </is>
+      </c>
+      <c r="B526" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND48-DR450</t>
+        </is>
+      </c>
       <c r="C526" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D526" s="12" t="inlineStr">
@@ -23693,39 +23665,43 @@
       </c>
       <c r="F526" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G526" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H526" s="12" t="n">
-        <v>864.0</v>
+        <v>4680.0</v>
       </c>
       <c r="I526" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J526" s="12" t="n">
-        <v>864.0</v>
+        <v>4680.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B527" s="12"/>
+          <t>GF0700000880</t>
+        </is>
+      </c>
+      <c r="B527" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR500-CFP</t>
+        </is>
+      </c>
       <c r="C527" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D527" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E527" s="12" t="inlineStr">
@@ -23735,39 +23711,43 @@
       </c>
       <c r="F527" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G527" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H527" s="12" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
       <c r="I527" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J527" s="12" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B528" s="12"/>
+          <t>GF0700000076</t>
+        </is>
+      </c>
+      <c r="B528" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505</t>
+        </is>
+      </c>
       <c r="C528" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D528" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E528" s="12" t="inlineStr">
@@ -23777,38 +23757,38 @@
       </c>
       <c r="F528" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G528" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H528" s="12" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
       <c r="I528" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J528" s="12" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
+          <t>GF0700000076</t>
         </is>
       </c>
       <c r="B529" s="12" t="inlineStr">
         <is>
-          <t>HSM-ND54-DR505-CFP</t>
+          <t>HSM-ND54-DR505</t>
         </is>
       </c>
       <c r="C529" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D529" s="12" t="inlineStr">
@@ -23823,12 +23803,12 @@
       </c>
       <c r="F529" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G529" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H529" s="12" t="n">
@@ -23844,10 +23824,14 @@
     <row r="530">
       <c r="A530" s="12" t="inlineStr">
         <is>
-          <t>GF0700002042</t>
-        </is>
-      </c>
-      <c r="B530" s="12"/>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B530" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505-CFP</t>
+        </is>
+      </c>
       <c r="C530" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -23855,7 +23839,7 @@
       </c>
       <c r="D530" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E530" s="12" t="inlineStr">
@@ -23865,19 +23849,19 @@
       </c>
       <c r="F530" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G530" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H530" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
       <c r="I530" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
       <c r="J530" s="12" t="n">
         <v>0.0</v>
@@ -23886,10 +23870,14 @@
     <row r="531">
       <c r="A531" s="12" t="inlineStr">
         <is>
-          <t>GF0700002065</t>
-        </is>
-      </c>
-      <c r="B531" s="12"/>
+          <t>GF0700001817</t>
+        </is>
+      </c>
+      <c r="B531" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND66-GR620</t>
+        </is>
+      </c>
       <c r="C531" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -23897,7 +23885,7 @@
       </c>
       <c r="D531" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E531" s="12" t="inlineStr">
@@ -23907,39 +23895,43 @@
       </c>
       <c r="F531" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G531" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H531" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
       <c r="I531" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J531" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="12" t="inlineStr">
         <is>
-          <t>GF0700002080</t>
-        </is>
-      </c>
-      <c r="B532" s="12"/>
+          <t>GF0101010096</t>
+        </is>
+      </c>
+      <c r="B532" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND66-GR625</t>
+        </is>
+      </c>
       <c r="C532" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D532" s="12" t="inlineStr">
         <is>
-          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E532" s="12" t="inlineStr">
@@ -23949,22 +23941,22 @@
       </c>
       <c r="F532" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G532" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H532" s="12" t="n">
-        <v>2160.0</v>
+        <v>0.0</v>
       </c>
       <c r="I532" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J532" s="12" t="n">
-        <v>2160.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="533">
@@ -23973,10 +23965,14 @@
           <t>GF0700001907</t>
         </is>
       </c>
-      <c r="B533" s="12"/>
+      <c r="B533" s="12" t="inlineStr">
+        <is>
+          <t>SPR-P7-515-BLK-P</t>
+        </is>
+      </c>
       <c r="C533" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D533" s="12" t="inlineStr">
@@ -23991,43 +23987,39 @@
       </c>
       <c r="F533" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G533" s="12" t="inlineStr">
         <is>
-          <t>2026 Week 44</t>
+          <t>2026 Week 43</t>
         </is>
       </c>
       <c r="H533" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
       <c r="I533" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
       <c r="J533" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="12" t="inlineStr">
         <is>
-          <t>GF0700000881</t>
-        </is>
-      </c>
-      <c r="B534" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505-CFP</t>
-        </is>
-      </c>
+          <t>GF0700001545</t>
+        </is>
+      </c>
+      <c r="B534" s="12"/>
       <c r="C534" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D534" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.4m,Silver Frame,White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E534" s="12" t="inlineStr">
@@ -24037,7 +24029,7 @@
       </c>
       <c r="F534" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G534" s="12" t="inlineStr">
@@ -24046,34 +24038,30 @@
         </is>
       </c>
       <c r="H534" s="12" t="n">
-        <v>864.0</v>
+        <v>1440.0</v>
       </c>
       <c r="I534" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J534" s="12" t="n">
-        <v>864.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="12" t="inlineStr">
         <is>
-          <t>GF0700000078</t>
-        </is>
-      </c>
-      <c r="B535" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND48-DR450</t>
-        </is>
-      </c>
+          <t>GF0700001546</t>
+        </is>
+      </c>
+      <c r="B535" s="12"/>
       <c r="C535" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D535" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.4m,Silver Frame,White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E535" s="12" t="inlineStr">
@@ -24083,7 +24071,7 @@
       </c>
       <c r="F535" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G535" s="12" t="inlineStr">
@@ -24092,34 +24080,30 @@
         </is>
       </c>
       <c r="H535" s="12" t="n">
-        <v>4680.0</v>
+        <v>1440.0</v>
       </c>
       <c r="I535" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J535" s="12" t="n">
-        <v>4680.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="12" t="inlineStr">
         <is>
-          <t>GF0700000071</t>
-        </is>
-      </c>
-      <c r="B536" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR500</t>
-        </is>
-      </c>
+          <t>GF0101010096</t>
+        </is>
+      </c>
+      <c r="B536" s="12"/>
       <c r="C536" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D536" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
         </is>
       </c>
       <c r="E536" s="12" t="inlineStr">
@@ -24129,7 +24113,7 @@
       </c>
       <c r="F536" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G536" s="12" t="inlineStr">
@@ -24138,29 +24122,25 @@
         </is>
       </c>
       <c r="H536" s="12" t="n">
-        <v>0.0</v>
+        <v>3600.0</v>
       </c>
       <c r="I536" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J536" s="12" t="n">
-        <v>0.0</v>
+        <v>3600.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="12" t="inlineStr">
         <is>
-          <t>GF0700000880</t>
-        </is>
-      </c>
-      <c r="B537" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR500-CFP</t>
-        </is>
-      </c>
+          <t>GF0700000076</t>
+        </is>
+      </c>
+      <c r="B537" s="12"/>
       <c r="C537" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D537" s="12" t="inlineStr">
@@ -24175,7 +24155,7 @@
       </c>
       <c r="F537" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G537" s="12" t="inlineStr">
@@ -24184,34 +24164,30 @@
         </is>
       </c>
       <c r="H537" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="I537" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J537" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
-        </is>
-      </c>
-      <c r="B538" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505</t>
-        </is>
-      </c>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B538" s="12"/>
       <c r="C538" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D538" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E538" s="12" t="inlineStr">
@@ -24221,7 +24197,7 @@
       </c>
       <c r="F538" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G538" s="12" t="inlineStr">
@@ -24230,34 +24206,30 @@
         </is>
       </c>
       <c r="H538" s="12" t="n">
-        <v>0.0</v>
+        <v>792.0</v>
       </c>
       <c r="I538" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J538" s="12" t="n">
-        <v>0.0</v>
+        <v>792.0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="12" t="inlineStr">
         <is>
-          <t>GF0700000076</t>
-        </is>
-      </c>
-      <c r="B539" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND54-DR505</t>
-        </is>
-      </c>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B539" s="12"/>
       <c r="C539" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D539" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E539" s="12" t="inlineStr">
@@ -24267,7 +24239,7 @@
       </c>
       <c r="F539" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G539" s="12" t="inlineStr">
@@ -24276,13 +24248,13 @@
         </is>
       </c>
       <c r="H539" s="12" t="n">
-        <v>0.0</v>
+        <v>792.0</v>
       </c>
       <c r="I539" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J539" s="12" t="n">
-        <v>0.0</v>
+        <v>792.0</v>
       </c>
     </row>
     <row r="540">
@@ -24313,7 +24285,7 @@
       </c>
       <c r="F540" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G540" s="12" t="inlineStr">
@@ -24334,14 +24306,10 @@
     <row r="541">
       <c r="A541" s="12" t="inlineStr">
         <is>
-          <t>GF0700001817</t>
-        </is>
-      </c>
-      <c r="B541" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND66-GR620</t>
-        </is>
-      </c>
+          <t>GF0700001578</t>
+        </is>
+      </c>
+      <c r="B541" s="12"/>
       <c r="C541" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -24349,7 +24317,7 @@
       </c>
       <c r="D541" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>TOPCon+3-Cuts,±1.2m,Black Frame,White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E541" s="12" t="inlineStr">
@@ -24359,7 +24327,7 @@
       </c>
       <c r="F541" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G541" s="12" t="inlineStr">
@@ -24368,26 +24336,22 @@
         </is>
       </c>
       <c r="H541" s="12" t="n">
-        <v>0.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I541" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J541" s="12" t="n">
-        <v>0.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="12" t="inlineStr">
         <is>
-          <t>GF0700002032</t>
-        </is>
-      </c>
-      <c r="B542" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND66-GR620</t>
-        </is>
-      </c>
+          <t>GF0700002042</t>
+        </is>
+      </c>
+      <c r="B542" s="12"/>
       <c r="C542" s="12" t="inlineStr">
         <is>
           <t>Arrival Plan-SPTN(PVLFR024)</t>
@@ -24395,7 +24359,7 @@
       </c>
       <c r="D542" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial,E</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E542" s="12" t="inlineStr">
@@ -24405,7 +24369,7 @@
       </c>
       <c r="F542" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G542" s="12" t="inlineStr">
@@ -24414,34 +24378,30 @@
         </is>
       </c>
       <c r="H542" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="I542" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J542" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="12" t="inlineStr">
         <is>
-          <t>GF0101010096</t>
-        </is>
-      </c>
-      <c r="B543" s="12" t="inlineStr">
-        <is>
-          <t>HSM-ND66-GR625</t>
-        </is>
-      </c>
+          <t>GF0700002065</t>
+        </is>
+      </c>
+      <c r="B543" s="12"/>
       <c r="C543" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D543" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E543" s="12" t="inlineStr">
@@ -24451,7 +24411,7 @@
       </c>
       <c r="F543" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G543" s="12" t="inlineStr">
@@ -24460,34 +24420,30 @@
         </is>
       </c>
       <c r="H543" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="I543" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J543" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="12" t="inlineStr">
         <is>
-          <t>GF0700001907</t>
-        </is>
-      </c>
-      <c r="B544" s="12" t="inlineStr">
-        <is>
-          <t>SPR-P7-515-BLK-P</t>
-        </is>
-      </c>
+          <t>GF0700002080</t>
+        </is>
+      </c>
+      <c r="B544" s="12"/>
       <c r="C544" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D544" s="12" t="inlineStr">
         <is>
-          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
       <c r="E544" s="12" t="inlineStr">
@@ -24497,7 +24453,7 @@
       </c>
       <c r="F544" s="12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G544" s="12" t="inlineStr">
@@ -24506,54 +24462,770 @@
         </is>
       </c>
       <c r="H544" s="12" t="n">
-        <v>0.0</v>
+        <v>2160.0</v>
       </c>
       <c r="I544" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J544" s="12" t="n">
-        <v>0.0</v>
+        <v>2160.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="12" t="inlineStr">
         <is>
-          <t>GF0700002080</t>
+          <t>GF0700001907</t>
         </is>
       </c>
       <c r="B545" s="12"/>
       <c r="C545" s="12" t="inlineStr">
         <is>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
+        </is>
+      </c>
+      <c r="D545" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E545" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F545" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G545" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H545" s="12" t="n">
+        <v>1584.0</v>
+      </c>
+      <c r="I545" s="12" t="n">
+        <v>864.0</v>
+      </c>
+      <c r="J545" s="12" t="n">
+        <v>720.0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="12" t="inlineStr">
+        <is>
+          <t>GF0700002065</t>
+        </is>
+      </c>
+      <c r="B546" s="12"/>
+      <c r="C546" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D546" s="12" t="inlineStr">
+        <is>
+          <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E546" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F546" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G546" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H546" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+      <c r="I546" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J546" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B547" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505-CFP</t>
+        </is>
+      </c>
+      <c r="C547" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D547" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E547" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F547" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G547" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H547" s="12" t="n">
+        <v>864.0</v>
+      </c>
+      <c r="I547" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J547" s="12" t="n">
+        <v>864.0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="12" t="inlineStr">
+        <is>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B548" s="12"/>
+      <c r="C548" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
+        </is>
+      </c>
+      <c r="D548" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E548" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F548" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G548" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H548" s="12" t="n">
+        <v>792.0</v>
+      </c>
+      <c r="I548" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J548" s="12" t="n">
+        <v>792.0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000078</t>
+        </is>
+      </c>
+      <c r="B549" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND48-DR450</t>
+        </is>
+      </c>
+      <c r="C549" s="12" t="inlineStr">
+        <is>
           <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
-      <c r="D545" s="12" t="inlineStr">
+      <c r="D549" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E549" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F549" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G549" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H549" s="12" t="n">
+        <v>4680.0</v>
+      </c>
+      <c r="I549" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J549" s="12" t="n">
+        <v>4680.0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000071</t>
+        </is>
+      </c>
+      <c r="B550" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR500</t>
+        </is>
+      </c>
+      <c r="C550" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D550" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E550" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F550" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G550" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H550" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I550" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J550" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000880</t>
+        </is>
+      </c>
+      <c r="B551" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR500-CFP</t>
+        </is>
+      </c>
+      <c r="C551" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D551" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E551" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F551" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G551" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H551" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I551" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J551" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000076</t>
+        </is>
+      </c>
+      <c r="B552" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505</t>
+        </is>
+      </c>
+      <c r="C552" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D552" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E552" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F552" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G552" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H552" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I552" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J552" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000076</t>
+        </is>
+      </c>
+      <c r="B553" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505</t>
+        </is>
+      </c>
+      <c r="C553" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
+        </is>
+      </c>
+      <c r="D553" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E553" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F553" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G553" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H553" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I553" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J553" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="12" t="inlineStr">
+        <is>
+          <t>GF0700000881</t>
+        </is>
+      </c>
+      <c r="B554" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND54-DR505-CFP</t>
+        </is>
+      </c>
+      <c r="C554" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D554" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.2m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E554" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F554" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G554" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H554" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I554" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J554" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="12" t="inlineStr">
+        <is>
+          <t>GF0700001817</t>
+        </is>
+      </c>
+      <c r="B555" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND66-GR620</t>
+        </is>
+      </c>
+      <c r="C555" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D555" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E555" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F555" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G555" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H555" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I555" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J555" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="12" t="inlineStr">
+        <is>
+          <t>GF0700002032</t>
+        </is>
+      </c>
+      <c r="B556" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND66-GR620</t>
+        </is>
+      </c>
+      <c r="C556" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
+        </is>
+      </c>
+      <c r="D556" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial,E</t>
+        </is>
+      </c>
+      <c r="E556" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F556" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G556" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H556" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I556" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J556" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="12" t="inlineStr">
+        <is>
+          <t>GF0101010096</t>
+        </is>
+      </c>
+      <c r="B557" s="12" t="inlineStr">
+        <is>
+          <t>HSM-ND66-GR625</t>
+        </is>
+      </c>
+      <c r="C557" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
+        </is>
+      </c>
+      <c r="D557" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+Half-Cuts,±1.4m,Silver Frame,Transparent+Redirection Film,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E557" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F557" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G557" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H557" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I557" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J557" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="12" t="inlineStr">
+        <is>
+          <t>GF0700001907</t>
+        </is>
+      </c>
+      <c r="B558" s="12" t="inlineStr">
+        <is>
+          <t>SPR-P7-515-BLK-P</t>
+        </is>
+      </c>
+      <c r="C558" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
+        </is>
+      </c>
+      <c r="D558" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+3-Cuts,±1.35m,Black Frame,Black glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E558" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F558" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G558" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H558" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I558" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J558" s="12" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="12" t="inlineStr">
+        <is>
+          <t>GF0700001545</t>
+        </is>
+      </c>
+      <c r="B559" s="12"/>
+      <c r="C559" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
+        </is>
+      </c>
+      <c r="D559" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+3-Cuts,±1.4m,Silver Frame,White glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E559" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F559" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G559" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H559" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+      <c r="I559" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J559" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="12" t="inlineStr">
+        <is>
+          <t>GF0700001546</t>
+        </is>
+      </c>
+      <c r="B560" s="12"/>
+      <c r="C560" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
+        </is>
+      </c>
+      <c r="D560" s="12" t="inlineStr">
+        <is>
+          <t>TOPCon+3-Cuts,±1.4m,Silver Frame,White glazing,Bi-facial</t>
+        </is>
+      </c>
+      <c r="E560" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F560" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G560" s="12" t="inlineStr">
+        <is>
+          <t>2026 Week 44</t>
+        </is>
+      </c>
+      <c r="H560" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+      <c r="I560" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J560" s="12" t="n">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="12" t="inlineStr">
+        <is>
+          <t>GF0700002080</t>
+        </is>
+      </c>
+      <c r="B561" s="12"/>
+      <c r="C561" s="12" t="inlineStr">
+        <is>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
+        </is>
+      </c>
+      <c r="D561" s="12" t="inlineStr">
         <is>
           <t>BC+Half-Cuts,±1.4m,Silver Frame(L30*28),White glazing,Bi-facial</t>
         </is>
       </c>
-      <c r="E545" s="12" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="F545" s="12" t="inlineStr">
+      <c r="E561" s="12" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F561" s="12" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="G545" s="12" t="inlineStr">
+      <c r="G561" s="12" t="inlineStr">
         <is>
           <t>2026 Week 44</t>
         </is>
       </c>
-      <c r="H545" s="12" t="n">
+      <c r="H561" s="12" t="n">
         <v>720.0</v>
       </c>
-      <c r="I545" s="12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J545" s="12" t="n">
+      <c r="I561" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J561" s="12" t="n">
         <v>720.0</v>
       </c>
     </row>

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -137,7 +137,7 @@
   <dimension ref="A1:J561"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.0" customWidth="true"/>
+    <col min="1" max="1" width="24.0" customWidth="true"/>
     <col min="2" max="2" width="23.0" customWidth="true"/>
     <col min="3" max="3" width="31.0" customWidth="true"/>
     <col min="4" max="4" width="239.0" customWidth="true"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="H206" s="12" t="n">
-        <v>1728.0</v>
+        <v>864.0</v>
       </c>
       <c r="I206" s="12" t="n">
-        <v>1728.0</v>
+        <v>864.0</v>
       </c>
       <c r="J206" s="12" t="n">
         <v>0.0</v>
@@ -11843,10 +11843,10 @@
         <v>4320.0</v>
       </c>
       <c r="I257" s="12" t="n">
-        <v>4320.0</v>
+        <v>3456.0</v>
       </c>
       <c r="J257" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="258">
@@ -13371,10 +13371,10 @@
         <v>19008.0</v>
       </c>
       <c r="I291" s="12" t="n">
-        <v>12960.0</v>
+        <v>10368.0</v>
       </c>
       <c r="J291" s="12" t="n">
-        <v>6048.0</v>
+        <v>8640.0</v>
       </c>
     </row>
     <row r="292">
@@ -14707,10 +14707,10 @@
         <v>3456.0</v>
       </c>
       <c r="I321" s="12" t="n">
-        <v>3456.0</v>
+        <v>2592.0</v>
       </c>
       <c r="J321" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="322">
@@ -15855,10 +15855,10 @@
         <v>3960.0</v>
       </c>
       <c r="I347" s="12" t="n">
-        <v>3816.0</v>
+        <v>3780.0</v>
       </c>
       <c r="J347" s="12" t="n">
-        <v>144.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="348">
@@ -16413,10 +16413,10 @@
         <v>9504.0</v>
       </c>
       <c r="I360" s="12" t="n">
-        <v>5184.0</v>
+        <v>6912.0</v>
       </c>
       <c r="J360" s="12" t="n">
-        <v>4320.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="361">
@@ -21289,10 +21289,10 @@
         <v>1584.0</v>
       </c>
       <c r="I470" s="12" t="n">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="J470" s="12" t="n">
-        <v>1584.0</v>
+        <v>1404.0</v>
       </c>
     </row>
     <row r="471">
@@ -23165,10 +23165,10 @@
         <v>864.0</v>
       </c>
       <c r="I514" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="J514" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="515">
@@ -23505,10 +23505,10 @@
         <v>792.0</v>
       </c>
       <c r="I522" s="12" t="n">
-        <v>216.0</v>
+        <v>648.0</v>
       </c>
       <c r="J522" s="12" t="n">
-        <v>576.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="523">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -137,10 +137,10 @@
   <dimension ref="A1:J470"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.0" customWidth="true"/>
+    <col min="1" max="1" width="19.0" customWidth="true"/>
     <col min="2" max="2" width="23.0" customWidth="true"/>
     <col min="3" max="3" width="31.0" customWidth="true"/>
-    <col min="4" max="4" width="239.0" customWidth="true"/>
+    <col min="4" max="4" width="168.0" customWidth="true"/>
     <col min="5" max="5" width="13.0" customWidth="true"/>
     <col min="6" max="6" width="16.0" customWidth="true"/>
     <col min="7" max="7" width="16.0" customWidth="true"/>
@@ -4511,10 +4511,10 @@
         <v>19008.0</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>18144.0</v>
+        <v>19008.0</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -14927,10 +14927,10 @@
         <v>7128.0</v>
       </c>
       <c r="I331" s="12" t="n">
-        <v>2880.0</v>
+        <v>2376.0</v>
       </c>
       <c r="J331" s="12" t="n">
-        <v>4248.0</v>
+        <v>4752.0</v>
       </c>
     </row>
     <row r="332">
@@ -15351,10 +15351,10 @@
         <v>9360.0</v>
       </c>
       <c r="I341" s="12" t="n">
-        <v>1872.0</v>
+        <v>3744.0</v>
       </c>
       <c r="J341" s="12" t="n">
-        <v>7488.0</v>
+        <v>5616.0</v>
       </c>
     </row>
     <row r="342">
